--- a/data/trans_orig/IP16_n_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R-Habitat-trans_orig.xlsx
@@ -1064,12 +1064,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>17078</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15377</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>25042</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21927</t>
+          <t>22265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44420</t>
+          <t>44780</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18008</t>
+          <t>17923</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>18250</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31867</t>
+          <t>31638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>20442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29802</t>
+          <t>30318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23720</t>
+          <t>24075</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33274</t>
+          <t>32980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47249</t>
+          <t>46768</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60808</t>
+          <t>60612</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,07%</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -2408,12 +2408,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>19862</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26874</t>
+          <t>26952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2493,12 +2493,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20418</t>
+          <t>20587</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>23383</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41395</t>
+          <t>41746</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>69,25%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -3080,12 +3080,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15670</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19868</t>
+          <t>20415</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34084</t>
+          <t>32450</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18265</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26124</t>
+          <t>25588</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28314</t>
+          <t>29348</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41823</t>
+          <t>41612</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -3641,12 +3641,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -3752,12 +3752,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>32951</t>
+          <t>34063</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50649</t>
+          <t>50655</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>43576</t>
+          <t>43212</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>61837</t>
+          <t>61346</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>82124</t>
+          <t>81545</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>107989</t>
+          <t>106924</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>68180</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>85591</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>78111</t>
+          <t>77648</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>96121</t>
+          <t>95779</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>149411</t>
+          <t>150966</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>176006</t>
+          <t>177034</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -4545,12 +4545,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4656,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>10763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18895</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -4767,12 +4767,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18357</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>26668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23579</t>
+          <t>23596</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>31485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4817,12 +4817,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44405</t>
+          <t>44567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56290</t>
+          <t>56567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -5328,12 +5328,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15414</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -5439,12 +5439,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31434</t>
+          <t>31903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38881</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30982</t>
+          <t>30881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38286</t>
+          <t>38331</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5489,12 +5489,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65716</t>
+          <t>65990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76018</t>
+          <t>76073</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -6000,12 +6000,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6085,12 +6085,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>23153</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29878</t>
+          <t>29965</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29605</t>
+          <t>29574</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54674</t>
+          <t>54709</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64046</t>
+          <t>64108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -6672,12 +6672,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11214</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>19964</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -6783,12 +6783,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>30367</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38488</t>
+          <t>38687</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34757</t>
+          <t>34859</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43528</t>
+          <t>43258</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>68547</t>
+          <t>67308</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>79731</t>
+          <t>80013</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -7344,12 +7344,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>31162</t>
+          <t>31045</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>28244</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32700</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>54429</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>112126</t>
+          <t>112361</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>128045</t>
+          <t>128797</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>129147</t>
+          <t>128420</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>143563</t>
+          <t>143251</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>246546</t>
+          <t>246197</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>269301</t>
+          <t>268565</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -8248,12 +8248,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>554</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>778</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -8359,12 +8359,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19815</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>23805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17178</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23180</t>
+          <t>23398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8409,12 +8409,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39187</t>
+          <t>39111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46545</t>
+          <t>46397</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>16418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -9031,12 +9031,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31277</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38921</t>
+          <t>39009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31778</t>
+          <t>31323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38632</t>
+          <t>38545</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66424</t>
+          <t>65793</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76451</t>
+          <t>76017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -9592,12 +9592,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9627,12 +9627,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15028</t>
+          <t>14094</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -9703,12 +9703,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21063</t>
+          <t>21421</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26473</t>
+          <t>26533</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9718,12 +9718,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24373</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9753,12 +9753,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40393</t>
+          <t>41327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49653</t>
+          <t>49837</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9788,12 +9788,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -10264,12 +10264,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10279,12 +10279,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -10375,12 +10375,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24190</t>
+          <t>24515</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30997</t>
+          <t>31222</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24745</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29571</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50850</t>
+          <t>52026</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59720</t>
+          <t>59968</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10895,12 +10895,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>533</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -10936,12 +10936,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22424</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10951,12 +10951,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>22777</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>40881</t>
+          <t>40095</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -11047,12 +11047,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>104533</t>
+          <t>104797</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>116166</t>
+          <t>117068</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11062,12 +11062,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11082,12 +11082,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>99141</t>
+          <t>98885</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>111589</t>
+          <t>111791</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>207705</t>
+          <t>208473</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>225509</t>
+          <t>225537</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11132,12 +11132,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -11840,12 +11840,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10901</t>
+          <t>10580</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11910,12 +11910,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>20358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11925,12 +11925,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -11951,12 +11951,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10763</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18995</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12021,12 +12021,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29462</t>
+          <t>30207</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40552</t>
+          <t>41072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12036,12 +12036,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -12401,12 +12401,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12451,12 +12451,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -12512,12 +12512,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12547,12 +12547,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>11208</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24141</t>
+          <t>22921</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>20691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37444</t>
+          <t>36923</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -12623,12 +12623,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>24375</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35926</t>
+          <t>36227</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12638,12 +12638,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35045</t>
+          <t>35261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47888</t>
+          <t>48403</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12673,12 +12673,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62370</t>
+          <t>63916</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80011</t>
+          <t>81662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13052,7 +13052,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -13073,12 +13073,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>447</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13088,12 +13088,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>402</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13143,12 +13143,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>11863</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13158,12 +13158,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -13184,12 +13184,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18863</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13219,12 +13219,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24154</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13234,12 +13234,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14636</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40872</t>
+          <t>39416</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13269,12 +13269,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -13295,12 +13295,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50156</t>
+          <t>49604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71664</t>
+          <t>72122</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13310,12 +13310,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13330,12 +13330,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30634</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43935</t>
+          <t>44266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13345,12 +13345,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13365,12 +13365,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85017</t>
+          <t>85075</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115205</t>
+          <t>117256</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13380,12 +13380,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13760,47 +13760,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>15,37%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2546</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5597</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>7,53%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>1,81%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>19,19%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>2546</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>5668</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13815,12 +13815,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -13856,12 +13856,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>12386</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13871,12 +13871,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13891,12 +13891,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13906,12 +13906,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13926,12 +13926,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24512</t>
+          <t>24499</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13941,12 +13941,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -13967,12 +13967,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23785</t>
+          <t>23845</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14002,12 +14002,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16514</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>25206</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14017,12 +14017,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14037,12 +14037,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>34221</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47056</t>
+          <t>47142</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14052,12 +14052,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,24%</t>
         </is>
       </c>
     </row>
@@ -14200,7 +14200,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -14306,12 +14306,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14391,12 +14391,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -14417,12 +14417,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -14452,12 +14452,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14487,12 +14487,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>26457</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -14528,12 +14528,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>53074</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14543,12 +14543,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14563,12 +14563,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>39978</t>
+          <t>40349</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>61853</t>
+          <t>61815</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14578,12 +14578,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14598,12 +14598,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>69490</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>106002</t>
+          <t>107821</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14613,12 +14613,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -14639,12 +14639,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>113248</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>147965</t>
+          <t>147134</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14654,12 +14654,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14674,12 +14674,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>108869</t>
+          <t>109441</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>132174</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14709,12 +14709,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>230866</t>
+          <t>229557</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>273932</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14724,12 +14724,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
